--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487677_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487677_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.6614</v>
+        <v>11.5107</v>
       </c>
       <c r="E2" t="n">
-        <v>6.912</v>
+        <v>4.9521</v>
       </c>
       <c r="F2" t="n">
-        <v>6.7494</v>
+        <v>6.5586</v>
       </c>
       <c r="G2" t="n">
         <v>6.6415</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3901</v>
+        <v>1.2393</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7568</v>
+        <v>0.7968</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6333</v>
+        <v>0.4425</v>
       </c>
       <c r="V2" t="n">
         <v>1.8836</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9691</v>
+        <v>8.036199999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6307</v>
+        <v>3.4525</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3384</v>
+        <v>4.5837</v>
       </c>
       <c r="G3" t="n">
         <v>4.1407</v>
@@ -688,13 +688,13 @@
         <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3775</v>
+        <v>-0.3104</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0655</v>
+        <v>-0.2437</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.312</v>
+        <v>-0.0667</v>
       </c>
       <c r="V3" t="n">
         <v>3.6238</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2854</v>
+        <v>5.7392</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8941</v>
+        <v>2.3751</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3914</v>
+        <v>3.3641</v>
       </c>
       <c r="G4" t="n">
         <v>2.4797</v>
@@ -766,13 +766,13 @@
         <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>0.952</v>
+        <v>0.4057</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0094</v>
+        <v>0.4904</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0574</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>1.8836</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3649</v>
+        <v>2.3141</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4189</v>
+        <v>-0.8974</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7838</v>
+        <v>3.2114</v>
       </c>
       <c r="G5" t="n">
         <v>0.2952</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2055</v>
+        <v>1.1547</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4599</v>
+        <v>0.0617</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6653</v>
+        <v>1.093</v>
       </c>
       <c r="V5" t="n">
         <v>0.2821</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5968</v>
+        <v>1.4609</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8047</v>
+        <v>-1.0224</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4015</v>
+        <v>2.4833</v>
       </c>
       <c r="G6" t="n">
         <v>2.8056</v>
@@ -922,13 +922,13 @@
         <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4311</v>
+        <v>0.4329</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8109</v>
+        <v>-0.0286</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3798</v>
+        <v>0.4616</v>
       </c>
       <c r="V6" t="n">
         <v>-2.1657</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4271</v>
+        <v>-0.7086</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7119</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.139</v>
+        <v>-1.5206</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7992</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2661</v>
+        <v>-0.0154</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2905</v>
+        <v>-0.1904</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5565</v>
+        <v>0.175</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2821</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2912</v>
+        <v>-0.7216</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.849</v>
+        <v>-0.7952</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4421</v>
+        <v>0.0737</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8789</v>
+        <v>1.9735</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0725</v>
+        <v>2.0308</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8064</v>
+        <v>-0.0573</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6673</v>
+        <v>1.3192</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.2152</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6673</v>
+        <v>0.104</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2115</v>
+        <v>0.6543</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0725</v>
+        <v>0.8156</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.139</v>
+        <v>-0.1613</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4123</v>
+        <v>-1.0831</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1817</v>
+        <v>-0.4562</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2306</v>
+        <v>-0.6269</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. PEÑA LOPEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,22 +1111,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3093</v>
+        <v>-1.1365</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.849</v>
+        <v>-0.7489</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4603</v>
+        <v>-0.3876</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1458</v>
+        <v>-0.8789</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.206</v>
+        <v>-0.0725</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9398</v>
+        <v>-0.8064</v>
       </c>
       <c r="J9" t="n">
         <v>-0.6673</v>
@@ -1138,13 +1138,13 @@
         <v>-0.6673</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4785</v>
+        <v>-0.2115</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.206</v>
+        <v>-0.0725</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2725</v>
+        <v>-0.139</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1635</v>
+        <v>-0.2577</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0182</v>
+        <v>-0.1761</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>F. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6157</v>
+        <v>-1.2821</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4169</v>
+        <v>-0.849</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1989</v>
+        <v>-0.433</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9735</v>
+        <v>-1.1458</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0308</v>
+        <v>-0.206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0573</v>
+        <v>-0.9398</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3192</v>
+        <v>-0.6673</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2152</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.104</v>
+        <v>-0.6673</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6543</v>
+        <v>-0.4785</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8156</v>
+        <v>-0.206</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1613</v>
+        <v>-0.2725</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5523</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9773</v>
+        <v>-0.1363</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0779</v>
+        <v>-0.1817</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8995</v>
+        <v>0.0454</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7228</v>
+        <v>-1.4259</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7759</v>
+        <v>-3.6153</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0531</v>
+        <v>2.1894</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9188</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3578</v>
+        <v>-0.0608</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5451</v>
+        <v>-0.3844</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1873</v>
+        <v>0.3236</v>
       </c>
       <c r="V11" t="n">
         <v>0.3299</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5927</v>
+        <v>-2.1684</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7034</v>
+        <v>-2.4427</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1107</v>
+        <v>0.2742</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4164</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9823</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4845</v>
+        <v>-0.2238</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4977</v>
+        <v>-0.3342</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0415</v>
+        <v>-2.5294</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6492</v>
+        <v>-3.3279</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6077</v>
+        <v>0.7985</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3566</v>
@@ -1468,13 +1468,13 @@
         <v>0.5821</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2968</v>
+        <v>0.2153</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3511</v>
+        <v>-0.0297</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0543</v>
+        <v>0.2451</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.8773</v>
+        <v>19.0886</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.3183</v>
+        <v>-2.1071</v>
       </c>
       <c r="F14" t="n">
         <v>21.1957</v>
@@ -1519,10 +1519,10 @@
         <v>-2.6414</v>
       </c>
       <c r="J14" t="n">
-        <v>4.718300000000003</v>
+        <v>4.718300000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.192399999999999</v>
+        <v>7.192400000000001</v>
       </c>
       <c r="L14" t="n">
         <v>-2.4743</v>
@@ -1546,13 +1546,13 @@
         <v>15.5226</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1849000000000006</v>
+        <v>1.0262</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.6826</v>
+        <v>-0.4712000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4975</v>
+        <v>1.4977</v>
       </c>
       <c r="V14" t="n">
         <v>4.331300000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4377</v>
+        <v>4.0716</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0657</v>
+        <v>2.5662</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3719</v>
+        <v>1.5054</v>
       </c>
       <c r="G15" t="n">
         <v>2.4202</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4004</v>
+        <v>0.2336</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7874</v>
+        <v>-0.2869</v>
       </c>
       <c r="U15" t="n">
-        <v>0.387</v>
+        <v>0.5204</v>
       </c>
       <c r="V15" t="n">
         <v>1.2239</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.253</v>
+        <v>2.3164</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3064</v>
+        <v>1.2063</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9465</v>
+        <v>1.11</v>
       </c>
       <c r="G16" t="n">
         <v>1.3914</v>
@@ -1702,13 +1702,13 @@
         <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2795</v>
+        <v>0.3429</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3039</v>
+        <v>0.2038</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0244</v>
+        <v>0.1391</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3959</v>
+        <v>1.2879</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2956</v>
+        <v>0.305</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6914</v>
+        <v>0.9828</v>
       </c>
       <c r="G17" t="n">
         <v>2.4913</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2431</v>
+        <v>0.6488</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5317</v>
+        <v>0.0689</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2885</v>
+        <v>0.5799</v>
       </c>
       <c r="V17" t="n">
         <v>0.2821</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>L. DE LA CRUZ DE LA ROSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8637</v>
+        <v>-0.8515</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6398</v>
+        <v>-1.6983</v>
       </c>
       <c r="F18" t="n">
-        <v>1.776</v>
+        <v>0.8468</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5515</v>
+        <v>-1.6613</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1116</v>
+        <v>-0.8955</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4399</v>
+        <v>-0.7658</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.2715</v>
+        <v>-1.2323</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.726</v>
+        <v>-0.6055</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5455</v>
+        <v>-0.6267</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.28</v>
+        <v>-0.429</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3856</v>
+        <v>-0.29</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1056</v>
+        <v>-0.139</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2131</v>
+        <v>-0.3544</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6213</v>
+        <v>-0.466</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5918</v>
+        <v>0.1116</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2716</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.9896</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. DE LA CRUZ DE LA ROSA</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9155</v>
+        <v>-1.2137</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8985</v>
+        <v>-0.5729</v>
       </c>
       <c r="F19" t="n">
-        <v>0.983</v>
+        <v>-0.6409</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6613</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8955</v>
+        <v>-1.5925</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7658</v>
+        <v>0.7079</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2323</v>
+        <v>-0.6556</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6055</v>
+        <v>-0.6962</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6267</v>
+        <v>0.0406</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.429</v>
+        <v>-0.229</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.29</v>
+        <v>-0.8964</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.139</v>
+        <v>0.6673</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4183</v>
+        <v>0.3126</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6662</v>
+        <v>0.0827</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2479</v>
+        <v>0.2299</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1137</v>
+        <v>-1.2393</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4728</v>
+        <v>-2.3865</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6409</v>
+        <v>1.1472</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8846000000000001</v>
+        <v>0.8889</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5925</v>
+        <v>-0.3295</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7079</v>
+        <v>1.2184</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6556</v>
+        <v>0.7231</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6962</v>
+        <v>0.033</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0406</v>
+        <v>0.6901</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.229</v>
+        <v>0.1658</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8964</v>
+        <v>-0.3625</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6673</v>
+        <v>0.5283</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5821</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4127</v>
+        <v>-0.0998</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1828</v>
+        <v>-0.1991</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2299</v>
+        <v>0.0993</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2543</v>
+        <v>-1.6246</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1863</v>
+        <v>-3.3405</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9319</v>
+        <v>1.7159</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8889</v>
+        <v>-2.5515</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3295</v>
+        <v>-2.1116</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2184</v>
+        <v>-0.4399</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7231</v>
+        <v>-2.2715</v>
       </c>
       <c r="K21" t="n">
-        <v>0.033</v>
+        <v>-1.726</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6901</v>
+        <v>-0.5455</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1658</v>
+        <v>-0.28</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3625</v>
+        <v>-0.3856</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5283</v>
+        <v>0.1056</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7463</v>
+        <v>1.7463</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1149</v>
+        <v>0.4523</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0011</v>
+        <v>-0.0794</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.116</v>
+        <v>0.5317</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2821</v>
+        <v>-1.2716</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.9896</v>
       </c>
       <c r="X21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7055</v>
+        <v>-2.2741</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5373</v>
+        <v>-2.5363</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1683</v>
+        <v>0.2622</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6215</v>
@@ -2170,13 +2170,13 @@
         <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4915</v>
+        <v>-0.06</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.6835</v>
+        <v>-0.6825</v>
       </c>
       <c r="U22" t="n">
-        <v>0.192</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.3776</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9589</v>
+        <v>-4.0473</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7515</v>
+        <v>-4.3521</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2075</v>
+        <v>0.3048</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7592</v>
@@ -2248,13 +2248,13 @@
         <v>1.3582</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6256</v>
+        <v>0.5372</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1168</v>
+        <v>0.3954</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2134</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6016</v>
+        <v>-4.2796</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5938</v>
+        <v>-4.8931</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0078</v>
+        <v>0.6135</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5133</v>
@@ -2326,13 +2326,13 @@
         <v>1.3582</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7882</v>
+        <v>-0.4663</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3201</v>
+        <v>-0.6194</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4681</v>
+        <v>0.1531</v>
       </c>
       <c r="V24" t="n">
         <v>0.2821</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5506</v>
+        <v>-8.021000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1926</v>
+        <v>-5.4939</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.358</v>
+        <v>-2.5272</v>
       </c>
       <c r="G25" t="n">
         <v>-5.0208</v>
@@ -2404,13 +2404,13 @@
         <v>0.7761</v>
       </c>
       <c r="S25" t="n">
-        <v>2.1106</v>
+        <v>0.6401</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6397</v>
+        <v>0.3384</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4709</v>
+        <v>0.3017</v>
       </c>
       <c r="V25" t="n">
         <v>-1.506</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.8772</v>
+        <v>-15.8752</v>
       </c>
       <c r="E26" t="n">
         <v>-21.1961</v>
       </c>
       <c r="F26" t="n">
-        <v>3.3182</v>
+        <v>5.320500000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-10.8204</v>
@@ -2452,7 +2452,7 @@
         <v>-13.4618</v>
       </c>
       <c r="I26" t="n">
-        <v>2.641500000000002</v>
+        <v>2.6415</v>
       </c>
       <c r="J26" t="n">
         <v>-6.102400000000001</v>
@@ -2461,7 +2461,7 @@
         <v>-6.269500000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1673000000000004</v>
+        <v>0.1672999999999996</v>
       </c>
       <c r="M26" t="n">
         <v>-4.718</v>
@@ -2482,13 +2482,13 @@
         <v>12.612</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1850999999999998</v>
+        <v>2.187</v>
       </c>
       <c r="T26" t="n">
         <v>-1.4977</v>
       </c>
       <c r="U26" t="n">
-        <v>1.6827</v>
+        <v>3.684599999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-4.331300000000001</v>
